--- a/data_input/density_class_combo_emissions.xlsx
+++ b/data_input/density_class_combo_emissions.xlsx
@@ -477,19 +477,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6836.521265689447</v>
+        <v>5885.438713979452</v>
       </c>
       <c r="D2" t="n">
-        <v>4476.425445977616</v>
+        <v>3815.326299624254</v>
       </c>
       <c r="E2" t="n">
-        <v>5386.228309513915</v>
+        <v>4356.990681273705</v>
       </c>
       <c r="F2" t="n">
-        <v>5521.350832673723</v>
+        <v>4603.686594037779</v>
       </c>
       <c r="G2" t="n">
-        <v>2206220</v>
+        <v>2254475</v>
       </c>
     </row>
     <row r="3">
@@ -504,19 +504,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8198.664246285654</v>
+        <v>7022.35421696803</v>
       </c>
       <c r="D3" t="n">
-        <v>4545.758814181378</v>
+        <v>3630.09418701205</v>
       </c>
       <c r="E3" t="n">
-        <v>6287.423206663882</v>
+        <v>4945.394340895863</v>
       </c>
       <c r="F3" t="n">
-        <v>6329.817368448697</v>
+        <v>5135.809271442951</v>
       </c>
       <c r="G3" t="n">
-        <v>161665</v>
+        <v>183240</v>
       </c>
     </row>
     <row r="4">
@@ -531,19 +531,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6561.570523684385</v>
+        <v>4798.163975956058</v>
       </c>
       <c r="D4" t="n">
-        <v>3310.955528946273</v>
+        <v>2755.057301259241</v>
       </c>
       <c r="E4" t="n">
-        <v>4252.569983103149</v>
+        <v>3587.449069498815</v>
       </c>
       <c r="F4" t="n">
-        <v>4594.416504709239</v>
+        <v>3682.029854053232</v>
       </c>
       <c r="G4" t="n">
-        <v>655420</v>
+        <v>629555</v>
       </c>
     </row>
     <row r="5">
@@ -558,19 +558,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7149.382960972376</v>
+        <v>6856.560316007463</v>
       </c>
       <c r="D5" t="n">
-        <v>4789.753746373264</v>
+        <v>4517.508062458724</v>
       </c>
       <c r="E5" t="n">
-        <v>5556.250602596017</v>
+        <v>4979.940841848915</v>
       </c>
       <c r="F5" t="n">
-        <v>5762.909478134419</v>
+        <v>5333.487515541005</v>
       </c>
       <c r="G5" t="n">
-        <v>2079560</v>
+        <v>2077660</v>
       </c>
     </row>
     <row r="6">
@@ -585,19 +585,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7658.941041718369</v>
+        <v>6875.952690843332</v>
       </c>
       <c r="D6" t="n">
-        <v>4615.648081507752</v>
+        <v>3891.541550423678</v>
       </c>
       <c r="E6" t="n">
-        <v>6532.310899975022</v>
+        <v>5633.779993692066</v>
       </c>
       <c r="F6" t="n">
-        <v>6334.802730794041</v>
+        <v>5508.763557162785</v>
       </c>
       <c r="G6" t="n">
-        <v>129535</v>
+        <v>135380</v>
       </c>
     </row>
     <row r="7">
@@ -612,19 +612,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5450.814615610396</v>
+        <v>5490.845356833731</v>
       </c>
       <c r="D7" t="n">
-        <v>3542.796449406331</v>
+        <v>3441.688371424738</v>
       </c>
       <c r="E7" t="n">
-        <v>4723.985430401611</v>
+        <v>4502.323700768236</v>
       </c>
       <c r="F7" t="n">
-        <v>4610.395481454987</v>
+        <v>4484.295282448736</v>
       </c>
       <c r="G7" t="n">
-        <v>459770</v>
+        <v>442365</v>
       </c>
     </row>
     <row r="8">
@@ -639,19 +639,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6424.390031906311</v>
+        <v>5811.008847314267</v>
       </c>
       <c r="D8" t="n">
-        <v>5280.767692124763</v>
+        <v>4854.986454913957</v>
       </c>
       <c r="E8" t="n">
-        <v>5977.472466524314</v>
+        <v>5233.68324629469</v>
       </c>
       <c r="F8" t="n">
-        <v>5915.025664269926</v>
+        <v>5283.3404487044</v>
       </c>
       <c r="G8" t="n">
-        <v>2128380</v>
+        <v>2156355</v>
       </c>
     </row>
     <row r="9">
@@ -666,19 +666,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>11944.58732442599</v>
+        <v>6706.930190072303</v>
       </c>
       <c r="D9" t="n">
-        <v>8893.106943405837</v>
+        <v>4579.438194532134</v>
       </c>
       <c r="E9" t="n">
-        <v>10221.39694004602</v>
+        <v>5996.25455248341</v>
       </c>
       <c r="F9" t="n">
-        <v>10320.12203698096</v>
+        <v>5819.719372392814</v>
       </c>
       <c r="G9" t="n">
-        <v>154085</v>
+        <v>155555</v>
       </c>
     </row>
     <row r="10">
@@ -693,19 +693,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6861.832087408879</v>
+        <v>5991.233202686336</v>
       </c>
       <c r="D10" t="n">
-        <v>4387.595644991877</v>
+        <v>3860.128216891741</v>
       </c>
       <c r="E10" t="n">
-        <v>5494.482334467484</v>
+        <v>5078.548332588484</v>
       </c>
       <c r="F10" t="n">
-        <v>5559.598100333931</v>
+        <v>5002.114521188762</v>
       </c>
       <c r="G10" t="n">
-        <v>264945</v>
+        <v>248880</v>
       </c>
     </row>
     <row r="11">
@@ -720,19 +720,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6328.114691664112</v>
+        <v>5585.02341419302</v>
       </c>
       <c r="D11" t="n">
-        <v>4218.698378481555</v>
+        <v>3642.814579523156</v>
       </c>
       <c r="E11" t="n">
-        <v>5239.530649475429</v>
+        <v>4326.264742248695</v>
       </c>
       <c r="F11" t="n">
-        <v>5256.468592274131</v>
+        <v>4470.091869553392</v>
       </c>
       <c r="G11" t="n">
-        <v>2674030</v>
+        <v>2688645</v>
       </c>
     </row>
     <row r="12">
@@ -747,19 +747,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>8770.579914911623</v>
+        <v>8208.365989629841</v>
       </c>
       <c r="D12" t="n">
-        <v>4455.75129493658</v>
+        <v>4116.620398576352</v>
       </c>
       <c r="E12" t="n">
-        <v>5734.383710311735</v>
+        <v>5263.093465643761</v>
       </c>
       <c r="F12" t="n">
-        <v>6173.774657617918</v>
+        <v>5712.79332987343</v>
       </c>
       <c r="G12" t="n">
-        <v>301050</v>
+        <v>333340</v>
       </c>
     </row>
     <row r="13">
@@ -774,19 +774,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6696.388540639855</v>
+        <v>5929.426064892786</v>
       </c>
       <c r="D13" t="n">
-        <v>2884.630550941538</v>
+        <v>2555.855974029972</v>
       </c>
       <c r="E13" t="n">
-        <v>3585.599387005332</v>
+        <v>3243.709742277852</v>
       </c>
       <c r="F13" t="n">
-        <v>4188.054466398014</v>
+        <v>3743.175380869615</v>
       </c>
       <c r="G13" t="n">
-        <v>1181240</v>
+        <v>1154980</v>
       </c>
     </row>
     <row r="14">
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5306.276426189853</v>
+        <v>4468.895865610992</v>
       </c>
       <c r="D14" t="n">
-        <v>3778.160582000226</v>
+        <v>3334.619606783634</v>
       </c>
       <c r="E14" t="n">
-        <v>4531.975372367494</v>
+        <v>4051.884041148074</v>
       </c>
       <c r="F14" t="n">
-        <v>4537.096938231267</v>
+        <v>3976.820888672693</v>
       </c>
       <c r="G14" t="n">
-        <v>1598165</v>
+        <v>1732915</v>
       </c>
     </row>
     <row r="15">
@@ -828,19 +828,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>10987.49189854286</v>
+        <v>9377.689862340778</v>
       </c>
       <c r="D15" t="n">
-        <v>5238.971610431654</v>
+        <v>4237.505181626087</v>
       </c>
       <c r="E15" t="n">
-        <v>6074.731382737433</v>
+        <v>4699.19515688581</v>
       </c>
       <c r="F15" t="n">
-        <v>7093.981568612345</v>
+        <v>5753.396339434621</v>
       </c>
       <c r="G15" t="n">
-        <v>540355</v>
+        <v>684640</v>
       </c>
     </row>
     <row r="16">
@@ -855,19 +855,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>7523.491433603667</v>
+        <v>6263.467842375323</v>
       </c>
       <c r="D16" t="n">
-        <v>2825.294882776402</v>
+        <v>2396.895055655953</v>
       </c>
       <c r="E16" t="n">
-        <v>3249.792891028198</v>
+        <v>2859.941984478597</v>
       </c>
       <c r="F16" t="n">
-        <v>4212.093024609116</v>
+        <v>3595.061716747118</v>
       </c>
       <c r="G16" t="n">
-        <v>1281440</v>
+        <v>1361870</v>
       </c>
     </row>
   </sheetData>

--- a/data_input/density_class_combo_emissions.xlsx
+++ b/data_input/density_class_combo_emissions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,7 +436,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>tenure_lab</t>
+          <t>inc_lab</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -473,23 +473,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>owner occupied</t>
+          <t>51-90%</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5885.438713979452</v>
+        <v>5239.881575399763</v>
       </c>
       <c r="D2" t="n">
-        <v>3815.326299624254</v>
+        <v>3606.039305736101</v>
       </c>
       <c r="E2" t="n">
-        <v>4356.990681273705</v>
+        <v>4027.631540995803</v>
       </c>
       <c r="F2" t="n">
-        <v>4603.686594037779</v>
+        <v>4225.295990781868</v>
       </c>
       <c r="G2" t="n">
-        <v>2254475</v>
+        <v>1460025</v>
       </c>
     </row>
     <row r="3">
@@ -500,23 +500,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>priate rental</t>
+          <t>91-99%</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7022.35421696803</v>
+        <v>6296.499469910782</v>
       </c>
       <c r="D3" t="n">
-        <v>3630.09418701205</v>
+        <v>4606.05448554169</v>
       </c>
       <c r="E3" t="n">
-        <v>4945.394340895863</v>
+        <v>4945.966629610308</v>
       </c>
       <c r="F3" t="n">
-        <v>5135.809271442951</v>
+        <v>5198.621803668272</v>
       </c>
       <c r="G3" t="n">
-        <v>183240</v>
+        <v>321830</v>
       </c>
     </row>
     <row r="4">
@@ -527,50 +527,50 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>social rental</t>
+          <t>poorest 50%</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4798.163975956058</v>
+        <v>4147.878472864532</v>
       </c>
       <c r="D4" t="n">
-        <v>2755.057301259241</v>
+        <v>2930.664823023083</v>
       </c>
       <c r="E4" t="n">
-        <v>3587.449069498815</v>
+        <v>3708.697259251159</v>
       </c>
       <c r="F4" t="n">
-        <v>3682.029854053232</v>
+        <v>3623.984453597483</v>
       </c>
       <c r="G4" t="n">
-        <v>629555</v>
+        <v>1254925</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>low suburban</t>
+          <t>high suburban</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>owner occupied</t>
+          <t>top 1%</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6856.560316007463</v>
+        <v>7839.256496930972</v>
       </c>
       <c r="D5" t="n">
-        <v>4517.508062458724</v>
+        <v>5818.351726334409</v>
       </c>
       <c r="E5" t="n">
-        <v>4979.940841848915</v>
+        <v>6274.560713722933</v>
       </c>
       <c r="F5" t="n">
-        <v>5333.487515541005</v>
+        <v>6551.682412677812</v>
       </c>
       <c r="G5" t="n">
-        <v>2077660</v>
+        <v>31610</v>
       </c>
     </row>
     <row r="6">
@@ -581,23 +581,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>priate rental</t>
+          <t>51-90%</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6875.952690843332</v>
+        <v>6478.397137832225</v>
       </c>
       <c r="D6" t="n">
-        <v>3891.541550423678</v>
+        <v>4515.5740240542</v>
       </c>
       <c r="E6" t="n">
-        <v>5633.779993692066</v>
+        <v>4791.567699257903</v>
       </c>
       <c r="F6" t="n">
-        <v>5508.763557162785</v>
+        <v>5144.276640100557</v>
       </c>
       <c r="G6" t="n">
-        <v>135380</v>
+        <v>1300790</v>
       </c>
     </row>
     <row r="7">
@@ -608,77 +608,77 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>social rental</t>
+          <t>91-99%</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5490.845356833731</v>
+        <v>6985.978957389824</v>
       </c>
       <c r="D7" t="n">
-        <v>3441.688371424738</v>
+        <v>5145.39500620411</v>
       </c>
       <c r="E7" t="n">
-        <v>4502.323700768236</v>
+        <v>5446.707908948989</v>
       </c>
       <c r="F7" t="n">
-        <v>4484.295282448736</v>
+        <v>5756.197445372978</v>
       </c>
       <c r="G7" t="n">
-        <v>442365</v>
+        <v>299315</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>rural</t>
+          <t>low suburban</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>owner occupied</t>
+          <t>poorest 50%</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5811.008847314267</v>
+        <v>4975.821285061419</v>
       </c>
       <c r="D8" t="n">
-        <v>4854.986454913957</v>
+        <v>3402.441236111623</v>
       </c>
       <c r="E8" t="n">
-        <v>5233.68324629469</v>
+        <v>4106.182121580295</v>
       </c>
       <c r="F8" t="n">
-        <v>5283.3404487044</v>
+        <v>4147.656691083408</v>
       </c>
       <c r="G8" t="n">
-        <v>2156355</v>
+        <v>1022635</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>rural</t>
+          <t>low suburban</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>priate rental</t>
+          <t>top 1%</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6706.930190072303</v>
+        <v>5891.795033361172</v>
       </c>
       <c r="D9" t="n">
-        <v>4579.438194532134</v>
+        <v>4849.432684221696</v>
       </c>
       <c r="E9" t="n">
-        <v>5996.25455248341</v>
+        <v>5136.783923530994</v>
       </c>
       <c r="F9" t="n">
-        <v>5819.719372392814</v>
+        <v>5253.698891161213</v>
       </c>
       <c r="G9" t="n">
-        <v>155555</v>
+        <v>33240</v>
       </c>
     </row>
     <row r="10">
@@ -689,185 +689,320 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>social rental</t>
+          <t>51-90%</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5991.233202686336</v>
+        <v>5012.11485654138</v>
       </c>
       <c r="D10" t="n">
-        <v>3860.128216891741</v>
+        <v>4483.367434927012</v>
       </c>
       <c r="E10" t="n">
-        <v>5078.548332588484</v>
+        <v>4638.513400104408</v>
       </c>
       <c r="F10" t="n">
-        <v>5002.114521188762</v>
+        <v>4693.127272919302</v>
       </c>
       <c r="G10" t="n">
-        <v>248880</v>
+        <v>1252035</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>urban</t>
+          <t>rural</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>owner occupied</t>
+          <t>91-99%</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5585.02341419302</v>
+        <v>5954.567676114597</v>
       </c>
       <c r="D11" t="n">
-        <v>3642.814579523156</v>
+        <v>5752.025447409799</v>
       </c>
       <c r="E11" t="n">
-        <v>4326.264742248695</v>
+        <v>5827.566164099035</v>
       </c>
       <c r="F11" t="n">
-        <v>4470.091869553392</v>
+        <v>5840.431362930617</v>
       </c>
       <c r="G11" t="n">
-        <v>2688645</v>
+        <v>338570</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>urban</t>
+          <t>rural</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>priate rental</t>
+          <t>poorest 50%</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>8208.365989629841</v>
+        <v>5596.44071680236</v>
       </c>
       <c r="D12" t="n">
-        <v>4116.620398576352</v>
+        <v>4154.099087841259</v>
       </c>
       <c r="E12" t="n">
-        <v>5263.093465643761</v>
+        <v>4732.341014569944</v>
       </c>
       <c r="F12" t="n">
-        <v>5712.79332987343</v>
+        <v>4803.805458445877</v>
       </c>
       <c r="G12" t="n">
-        <v>333340</v>
+        <v>931530</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>urban</t>
+          <t>rural</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>social rental</t>
+          <t>top 1%</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5929.426064892786</v>
+        <v>6025.837878424099</v>
       </c>
       <c r="D13" t="n">
-        <v>2555.855974029972</v>
+        <v>5725.861715738954</v>
       </c>
       <c r="E13" t="n">
-        <v>3243.709742277852</v>
+        <v>5888.829784664998</v>
       </c>
       <c r="F13" t="n">
-        <v>3743.175380869615</v>
+        <v>5882.339790873262</v>
       </c>
       <c r="G13" t="n">
-        <v>1154980</v>
+        <v>39515</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>very urban</t>
+          <t>urban</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>owner occupied</t>
+          <t>51-90%</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4468.895865610992</v>
+        <v>4991.343539869354</v>
       </c>
       <c r="D14" t="n">
-        <v>3334.619606783634</v>
+        <v>3440.4850817275</v>
       </c>
       <c r="E14" t="n">
-        <v>4051.884041148074</v>
+        <v>4022.01160596818</v>
       </c>
       <c r="F14" t="n">
-        <v>3976.820888672693</v>
+        <v>4118.962958383304</v>
       </c>
       <c r="G14" t="n">
-        <v>1732915</v>
+        <v>1834780</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>very urban</t>
+          <t>urban</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>priate rental</t>
+          <t>91-99%</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>9377.689862340778</v>
+        <v>6007.608793897572</v>
       </c>
       <c r="D15" t="n">
-        <v>4237.505181626087</v>
+        <v>4334.682567468236</v>
       </c>
       <c r="E15" t="n">
-        <v>4699.19515688581</v>
+        <v>4850.112221345489</v>
       </c>
       <c r="F15" t="n">
-        <v>5753.396339434621</v>
+        <v>5010.628951014196</v>
       </c>
       <c r="G15" t="n">
-        <v>684640</v>
+        <v>400205</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>urban</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>poorest 50%</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>3964.217565699944</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2672.676401078681</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3350.080688988018</v>
+      </c>
+      <c r="F16" t="n">
+        <v>3334.263836188665</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1905790</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>urban</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>top 1%</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>10641.42374291252</v>
+      </c>
+      <c r="D17" t="n">
+        <v>8124.520216181863</v>
+      </c>
+      <c r="E17" t="n">
+        <v>8603.13973200349</v>
+      </c>
+      <c r="F17" t="n">
+        <v>8993.055855775339</v>
+      </c>
+      <c r="G17" t="n">
+        <v>37940</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>very urban</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>social rental</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>6263.467842375323</v>
-      </c>
-      <c r="D16" t="n">
-        <v>2396.895055655953</v>
-      </c>
-      <c r="E16" t="n">
-        <v>2859.941984478597</v>
-      </c>
-      <c r="F16" t="n">
-        <v>3595.061716747118</v>
-      </c>
-      <c r="G16" t="n">
-        <v>1361870</v>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>51-90%</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>3742.633389894152</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2848.904155705424</v>
+      </c>
+      <c r="E18" t="n">
+        <v>3391.898215711025</v>
+      </c>
+      <c r="F18" t="n">
+        <v>3343.833494255407</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1418650</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>very urban</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>91-99%</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>4618.428265112355</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3616.504143300569</v>
+      </c>
+      <c r="E19" t="n">
+        <v>4208.725913126018</v>
+      </c>
+      <c r="F19" t="n">
+        <v>4163.09605866624</v>
+      </c>
+      <c r="G19" t="n">
+        <v>392465</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>very urban</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>poorest 50%</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>3730.869870779442</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2455.158334517435</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2852.937627357822</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2972.97586500313</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1925210</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>very urban</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>top 1%</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>7396.817729346041</v>
+      </c>
+      <c r="D21" t="n">
+        <v>6489.808354723963</v>
+      </c>
+      <c r="E21" t="n">
+        <v>7069.494470871497</v>
+      </c>
+      <c r="F21" t="n">
+        <v>7006.40375645325</v>
+      </c>
+      <c r="G21" t="n">
+        <v>46530</v>
       </c>
     </row>
   </sheetData>

--- a/data_input/density_class_combo_emissions.xlsx
+++ b/data_input/density_class_combo_emissions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,23 +473,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>51-90%</t>
+          <t>decile 1 (poorest)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5239.881575399763</v>
+        <v>4001.184702549341</v>
       </c>
       <c r="D2" t="n">
-        <v>3606.039305736101</v>
+        <v>2334.51534600951</v>
       </c>
       <c r="E2" t="n">
-        <v>4027.631540995803</v>
+        <v>3015.246253541585</v>
       </c>
       <c r="F2" t="n">
-        <v>4225.295990781868</v>
+        <v>3091.548138910505</v>
       </c>
       <c r="G2" t="n">
-        <v>1460025</v>
+        <v>200440</v>
       </c>
     </row>
     <row r="3">
@@ -500,23 +500,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>91-99%</t>
+          <t>decile 10 (richest)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6296.499469910782</v>
+        <v>6397.304732007802</v>
       </c>
       <c r="D3" t="n">
-        <v>4606.05448554169</v>
+        <v>4661.161182050686</v>
       </c>
       <c r="E3" t="n">
-        <v>4945.966629610308</v>
+        <v>5055.575774458283</v>
       </c>
       <c r="F3" t="n">
-        <v>5198.621803668272</v>
+        <v>5292.404365743763</v>
       </c>
       <c r="G3" t="n">
-        <v>321830</v>
+        <v>353545</v>
       </c>
     </row>
     <row r="4">
@@ -527,23 +527,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>poorest 50%</t>
+          <t>decile 2</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4147.878472864532</v>
+        <v>3830.670156409551</v>
       </c>
       <c r="D4" t="n">
-        <v>2930.664823023083</v>
+        <v>2708.586906054574</v>
       </c>
       <c r="E4" t="n">
-        <v>3708.697259251159</v>
+        <v>3297.776466878449</v>
       </c>
       <c r="F4" t="n">
-        <v>3623.984453597483</v>
+        <v>3283.702499055256</v>
       </c>
       <c r="G4" t="n">
-        <v>1254925</v>
+        <v>217030</v>
       </c>
     </row>
     <row r="5">
@@ -554,455 +554,1265 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>top 1%</t>
+          <t>decile 3</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7839.256496930972</v>
+        <v>4066.991989777974</v>
       </c>
       <c r="D5" t="n">
-        <v>5818.351726334409</v>
+        <v>2977.546571877547</v>
       </c>
       <c r="E5" t="n">
-        <v>6274.560713722933</v>
+        <v>3696.41459871549</v>
       </c>
       <c r="F5" t="n">
-        <v>6551.682412677812</v>
+        <v>3609.341939771625</v>
       </c>
       <c r="G5" t="n">
-        <v>31610</v>
+        <v>236770</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>low suburban</t>
+          <t>high suburban</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>51-90%</t>
+          <t>decile 4</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6478.397137832225</v>
+        <v>4920.498037600655</v>
       </c>
       <c r="D6" t="n">
-        <v>4515.5740240542</v>
+        <v>3343.469276299834</v>
       </c>
       <c r="E6" t="n">
-        <v>4791.567699257903</v>
+        <v>4217.588117832442</v>
       </c>
       <c r="F6" t="n">
-        <v>5144.276640100557</v>
+        <v>4174.785887391343</v>
       </c>
       <c r="G6" t="n">
-        <v>1300790</v>
+        <v>283620</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>low suburban</t>
+          <t>high suburban</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>91-99%</t>
+          <t>decile 5</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6985.978957389824</v>
+        <v>4461.749876024409</v>
       </c>
       <c r="D7" t="n">
-        <v>5145.39500620411</v>
+        <v>3001.445312173605</v>
       </c>
       <c r="E7" t="n">
-        <v>5446.707908948989</v>
+        <v>3681.628512541232</v>
       </c>
       <c r="F7" t="n">
-        <v>5756.197445372978</v>
+        <v>3706.613053320119</v>
       </c>
       <c r="G7" t="n">
-        <v>299315</v>
+        <v>317015</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>low suburban</t>
+          <t>high suburban</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>poorest 50%</t>
+          <t>decile 6</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4975.821285061419</v>
+        <v>4770.212727629429</v>
       </c>
       <c r="D8" t="n">
-        <v>3402.441236111623</v>
+        <v>3180.911371072953</v>
       </c>
       <c r="E8" t="n">
-        <v>4106.182121580295</v>
+        <v>3766.636092256967</v>
       </c>
       <c r="F8" t="n">
-        <v>4147.656691083408</v>
+        <v>3871.099070804079</v>
       </c>
       <c r="G8" t="n">
-        <v>1022635</v>
+        <v>351080</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>low suburban</t>
+          <t>high suburban</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>top 1%</t>
+          <t>decile 7</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5891.795033361172</v>
+        <v>5099.690274979755</v>
       </c>
       <c r="D9" t="n">
-        <v>4849.432684221696</v>
+        <v>3492.902171789032</v>
       </c>
       <c r="E9" t="n">
-        <v>5136.783923530994</v>
+        <v>3955.530802460597</v>
       </c>
       <c r="F9" t="n">
-        <v>5253.698891161213</v>
+        <v>4125.913512922496</v>
       </c>
       <c r="G9" t="n">
-        <v>33240</v>
+        <v>363045</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>rural</t>
+          <t>high suburban</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>51-90%</t>
+          <t>decile 8</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5012.11485654138</v>
+        <v>5210.923695237904</v>
       </c>
       <c r="D10" t="n">
-        <v>4483.367434927012</v>
+        <v>3684.468382581227</v>
       </c>
       <c r="E10" t="n">
-        <v>4638.513400104408</v>
+        <v>4047.806947481906</v>
       </c>
       <c r="F10" t="n">
-        <v>4693.127272919302</v>
+        <v>4247.751493195736</v>
       </c>
       <c r="G10" t="n">
-        <v>1252035</v>
+        <v>372085</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>rural</t>
+          <t>high suburban</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>91-99%</t>
+          <t>decile 9</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5954.567676114597</v>
+        <v>5649.701614196071</v>
       </c>
       <c r="D11" t="n">
-        <v>5752.025447409799</v>
+        <v>4052.841171685796</v>
       </c>
       <c r="E11" t="n">
-        <v>5827.566164099035</v>
+        <v>4390.093168930343</v>
       </c>
       <c r="F11" t="n">
-        <v>5840.431362930617</v>
+        <v>4620.682280935639</v>
       </c>
       <c r="G11" t="n">
-        <v>338570</v>
+        <v>373785</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>rural</t>
+          <t>low suburban</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>poorest 50%</t>
+          <t>decile 1 (poorest)</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5596.44071680236</v>
+        <v>4482.968795188325</v>
       </c>
       <c r="D12" t="n">
-        <v>4154.099087841259</v>
+        <v>2745.113879639363</v>
       </c>
       <c r="E12" t="n">
-        <v>4732.341014569944</v>
+        <v>3652.909509970467</v>
       </c>
       <c r="F12" t="n">
-        <v>4803.805458445877</v>
+        <v>3633.475423692155</v>
       </c>
       <c r="G12" t="n">
-        <v>931530</v>
+        <v>146880</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>rural</t>
+          <t>low suburban</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>top 1%</t>
+          <t>decile 10 (richest)</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6025.837878424099</v>
+        <v>6949.841478606488</v>
       </c>
       <c r="D13" t="n">
-        <v>5725.861715738954</v>
+        <v>5126.07037602059</v>
       </c>
       <c r="E13" t="n">
-        <v>5888.829784664998</v>
+        <v>5479.834538997606</v>
       </c>
       <c r="F13" t="n">
-        <v>5882.339790873262</v>
+        <v>5758.895233155572</v>
       </c>
       <c r="G13" t="n">
-        <v>39515</v>
+        <v>332760</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>urban</t>
+          <t>low suburban</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>51-90%</t>
+          <t>decile 2</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4991.343539869354</v>
+        <v>4514.028403035381</v>
       </c>
       <c r="D14" t="n">
-        <v>3440.4850817275</v>
+        <v>3440.951977165368</v>
       </c>
       <c r="E14" t="n">
-        <v>4022.01160596818</v>
+        <v>4150.894049479665</v>
       </c>
       <c r="F14" t="n">
-        <v>4118.962958383304</v>
+        <v>4064.19211979002</v>
       </c>
       <c r="G14" t="n">
-        <v>1834780</v>
+        <v>169535</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>urban</t>
+          <t>low suburban</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>91-99%</t>
+          <t>decile 3</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6007.608793897572</v>
+        <v>4213.791384558198</v>
       </c>
       <c r="D15" t="n">
-        <v>4334.682567468236</v>
+        <v>3025.592008059352</v>
       </c>
       <c r="E15" t="n">
-        <v>4850.112221345489</v>
+        <v>3765.537500620754</v>
       </c>
       <c r="F15" t="n">
-        <v>5010.628951014196</v>
+        <v>3692.614598464765</v>
       </c>
       <c r="G15" t="n">
-        <v>400205</v>
+        <v>193740</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>urban</t>
+          <t>low suburban</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>poorest 50%</t>
+          <t>decile 4</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3964.217565699944</v>
+        <v>5363.639473101308</v>
       </c>
       <c r="D16" t="n">
-        <v>2672.676401078681</v>
+        <v>3630.580827021815</v>
       </c>
       <c r="E16" t="n">
-        <v>3350.080688988018</v>
+        <v>4436.140538938744</v>
       </c>
       <c r="F16" t="n">
-        <v>3334.263836188665</v>
+        <v>4466.625344500152</v>
       </c>
       <c r="G16" t="n">
-        <v>1905790</v>
+        <v>236925</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>urban</t>
+          <t>low suburban</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>top 1%</t>
+          <t>decile 5</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>10641.42374291252</v>
+        <v>5713.987681951315</v>
       </c>
       <c r="D17" t="n">
-        <v>8124.520216181863</v>
+        <v>3745.779503485046</v>
       </c>
       <c r="E17" t="n">
-        <v>8603.13973200349</v>
+        <v>4322.450755602216</v>
       </c>
       <c r="F17" t="n">
-        <v>8993.055855775339</v>
+        <v>4526.167174160199</v>
       </c>
       <c r="G17" t="n">
-        <v>37940</v>
+        <v>275575</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>very urban</t>
+          <t>low suburban</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>51-90%</t>
+          <t>decile 6</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3742.633389894152</v>
+        <v>5144.197027145095</v>
       </c>
       <c r="D18" t="n">
-        <v>2848.904155705424</v>
+        <v>3456.041345253037</v>
       </c>
       <c r="E18" t="n">
-        <v>3391.898215711025</v>
+        <v>3869.483444332718</v>
       </c>
       <c r="F18" t="n">
-        <v>3343.833494255407</v>
+        <v>4084.801315265892</v>
       </c>
       <c r="G18" t="n">
-        <v>1418650</v>
+        <v>306885</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>very urban</t>
+          <t>low suburban</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>91-99%</t>
+          <t>decile 7</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4618.428265112355</v>
+        <v>6393.752832412273</v>
       </c>
       <c r="D19" t="n">
-        <v>3616.504143300569</v>
+        <v>4427.64720888718</v>
       </c>
       <c r="E19" t="n">
-        <v>4208.725913126018</v>
+        <v>4713.889123999243</v>
       </c>
       <c r="F19" t="n">
-        <v>4163.09605866624</v>
+        <v>5062.294572324485</v>
       </c>
       <c r="G19" t="n">
-        <v>392465</v>
+        <v>323080</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>very urban</t>
+          <t>low suburban</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>poorest 50%</t>
+          <t>decile 8</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3730.869870779442</v>
+        <v>7471.834488895447</v>
       </c>
       <c r="D20" t="n">
-        <v>2455.158334517435</v>
+        <v>5330.366694522197</v>
       </c>
       <c r="E20" t="n">
-        <v>2852.937627357822</v>
+        <v>5525.227725102091</v>
       </c>
       <c r="F20" t="n">
-        <v>2972.97586500313</v>
+        <v>5963.164158405457</v>
       </c>
       <c r="G20" t="n">
-        <v>1925210</v>
+        <v>333560</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>low suburban</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>decile 9</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>6296.808282985407</v>
+      </c>
+      <c r="D21" t="n">
+        <v>4677.967262525334</v>
+      </c>
+      <c r="E21" t="n">
+        <v>4932.675391568439</v>
+      </c>
+      <c r="F21" t="n">
+        <v>5210.031582161904</v>
+      </c>
+      <c r="G21" t="n">
+        <v>337270</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>rural</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>decile 1 (poorest)</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>5299.685652077666</v>
+      </c>
+      <c r="D22" t="n">
+        <v>3460.734326983153</v>
+      </c>
+      <c r="E22" t="n">
+        <v>4523.505017204738</v>
+      </c>
+      <c r="F22" t="n">
+        <v>4451.857503367573</v>
+      </c>
+      <c r="G22" t="n">
+        <v>129775</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>rural</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>decile 10 (richest)</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>6044.486568191954</v>
+      </c>
+      <c r="D23" t="n">
+        <v>5803.112968791757</v>
+      </c>
+      <c r="E23" t="n">
+        <v>5868.93037514257</v>
+      </c>
+      <c r="F23" t="n">
+        <v>5896.365071817213</v>
+      </c>
+      <c r="G23" t="n">
+        <v>378330</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>rural</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>decile 2</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>4418.243659221745</v>
+      </c>
+      <c r="D24" t="n">
+        <v>3521.974924191022</v>
+      </c>
+      <c r="E24" t="n">
+        <v>4155.356484876476</v>
+      </c>
+      <c r="F24" t="n">
+        <v>4062.732888291429</v>
+      </c>
+      <c r="G24" t="n">
+        <v>141735</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>rural</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>decile 3</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>4671.895739999127</v>
+      </c>
+      <c r="D25" t="n">
+        <v>3568.875854252115</v>
+      </c>
+      <c r="E25" t="n">
+        <v>4210.988485830687</v>
+      </c>
+      <c r="F25" t="n">
+        <v>4165.687141478154</v>
+      </c>
+      <c r="G25" t="n">
+        <v>177580</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>rural</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>decile 4</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>5290.125471693559</v>
+      </c>
+      <c r="D26" t="n">
+        <v>3920.049801459709</v>
+      </c>
+      <c r="E26" t="n">
+        <v>4564.964164138566</v>
+      </c>
+      <c r="F26" t="n">
+        <v>4585.0259003576</v>
+      </c>
+      <c r="G26" t="n">
+        <v>225515</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>rural</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>decile 5</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>6450.748969703031</v>
+      </c>
+      <c r="D27" t="n">
+        <v>5061.699694363081</v>
+      </c>
+      <c r="E27" t="n">
+        <v>5385.726942057051</v>
+      </c>
+      <c r="F27" t="n">
+        <v>5570.975637045054</v>
+      </c>
+      <c r="G27" t="n">
+        <v>256895</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>rural</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>decile 6</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>5411.378954223218</v>
+      </c>
+      <c r="D28" t="n">
+        <v>4527.522688995416</v>
+      </c>
+      <c r="E28" t="n">
+        <v>4751.099308711322</v>
+      </c>
+      <c r="F28" t="n">
+        <v>4860.275065160319</v>
+      </c>
+      <c r="G28" t="n">
+        <v>287065</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>rural</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>decile 7</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>4559.289949905376</v>
+      </c>
+      <c r="D29" t="n">
+        <v>3988.054647111485</v>
+      </c>
+      <c r="E29" t="n">
+        <v>4194.716759922487</v>
+      </c>
+      <c r="F29" t="n">
+        <v>4234.194529215459</v>
+      </c>
+      <c r="G29" t="n">
+        <v>300400</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>rural</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>decile 8</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>4824.613578977552</v>
+      </c>
+      <c r="D30" t="n">
+        <v>4496.098254151388</v>
+      </c>
+      <c r="E30" t="n">
+        <v>4634.562125993309</v>
+      </c>
+      <c r="F30" t="n">
+        <v>4647.459021278889</v>
+      </c>
+      <c r="G30" t="n">
+        <v>321805</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>rural</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>decile 9</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>5057.111486514842</v>
+      </c>
+      <c r="D31" t="n">
+        <v>4785.631496597122</v>
+      </c>
+      <c r="E31" t="n">
+        <v>4905.093963966543</v>
+      </c>
+      <c r="F31" t="n">
+        <v>4913.232727761262</v>
+      </c>
+      <c r="G31" t="n">
+        <v>342730</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>urban</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>decile 1 (poorest)</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>4076.103939955301</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2256.984794817912</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2813.559805103208</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2990.052086244908</v>
+      </c>
+      <c r="G32" t="n">
+        <v>371845</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>urban</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>decile 10 (richest)</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>6247.778002951329</v>
+      </c>
+      <c r="D33" t="n">
+        <v>4531.038702487694</v>
+      </c>
+      <c r="E33" t="n">
+        <v>5075.998606526915</v>
+      </c>
+      <c r="F33" t="n">
+        <v>5232.703479623213</v>
+      </c>
+      <c r="G33" t="n">
+        <v>438150</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>urban</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>decile 2</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>3894.817204797086</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2676.536766847161</v>
+      </c>
+      <c r="E34" t="n">
+        <v>3229.401276861377</v>
+      </c>
+      <c r="F34" t="n">
+        <v>3257.53913134175</v>
+      </c>
+      <c r="G34" t="n">
+        <v>357245</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>urban</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>decile 3</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>3921.338106012824</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2701.969669125801</v>
+      </c>
+      <c r="E35" t="n">
+        <v>3373.059224053686</v>
+      </c>
+      <c r="F35" t="n">
+        <v>3342.356555811499</v>
+      </c>
+      <c r="G35" t="n">
+        <v>360205</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>urban</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>decile 4</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>4142.584969270411</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2808.681515310225</v>
+      </c>
+      <c r="E36" t="n">
+        <v>3530.692152423388</v>
+      </c>
+      <c r="F36" t="n">
+        <v>3503.162697356853</v>
+      </c>
+      <c r="G36" t="n">
+        <v>394355</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>urban</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>decile 5</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>4200.352554492794</v>
+      </c>
+      <c r="D37" t="n">
+        <v>2891.018935775848</v>
+      </c>
+      <c r="E37" t="n">
+        <v>3697.638452672783</v>
+      </c>
+      <c r="F37" t="n">
+        <v>3621.662098903552</v>
+      </c>
+      <c r="G37" t="n">
+        <v>422135</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>urban</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>decile 6</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>4466.78434897479</v>
+      </c>
+      <c r="D38" t="n">
+        <v>3025.616193521877</v>
+      </c>
+      <c r="E38" t="n">
+        <v>3764.48342718909</v>
+      </c>
+      <c r="F38" t="n">
+        <v>3755.341849218712</v>
+      </c>
+      <c r="G38" t="n">
+        <v>444120</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>urban</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>decile 7</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>4843.198408758136</v>
+      </c>
+      <c r="D39" t="n">
+        <v>3281.350843245439</v>
+      </c>
+      <c r="E39" t="n">
+        <v>3951.022859406249</v>
+      </c>
+      <c r="F39" t="n">
+        <v>4006.648742704019</v>
+      </c>
+      <c r="G39" t="n">
+        <v>457095</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>urban</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>decile 8</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>5540.747439750973</v>
+      </c>
+      <c r="D40" t="n">
+        <v>3909.123715996295</v>
+      </c>
+      <c r="E40" t="n">
+        <v>4413.738306565785</v>
+      </c>
+      <c r="F40" t="n">
+        <v>4569.336942219709</v>
+      </c>
+      <c r="G40" t="n">
+        <v>467780</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>urban</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>decile 9</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>5015.333677536692</v>
+      </c>
+      <c r="D41" t="n">
+        <v>3585.462883494533</v>
+      </c>
+      <c r="E41" t="n">
+        <v>4082.324335309776</v>
+      </c>
+      <c r="F41" t="n">
+        <v>4191.361307912694</v>
+      </c>
+      <c r="G41" t="n">
+        <v>465810</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>very urban</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>top 1%</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>7396.817729346041</v>
-      </c>
-      <c r="D21" t="n">
-        <v>6489.808354723963</v>
-      </c>
-      <c r="E21" t="n">
-        <v>7069.494470871497</v>
-      </c>
-      <c r="F21" t="n">
-        <v>7006.40375645325</v>
-      </c>
-      <c r="G21" t="n">
-        <v>46530</v>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>decile 1 (poorest)</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>3908.904393004301</v>
+      </c>
+      <c r="D42" t="n">
+        <v>2101.120858799821</v>
+      </c>
+      <c r="E42" t="n">
+        <v>2382.295649375053</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2693.654137638557</v>
+      </c>
+      <c r="G42" t="n">
+        <v>530775</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>very urban</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>decile 10 (richest)</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>4896.879161977036</v>
+      </c>
+      <c r="D43" t="n">
+        <v>3860.202402977864</v>
+      </c>
+      <c r="E43" t="n">
+        <v>4464.161098215613</v>
+      </c>
+      <c r="F43" t="n">
+        <v>4421.350940346532</v>
+      </c>
+      <c r="G43" t="n">
+        <v>439235</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>very urban</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>decile 2</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>3751.54886416195</v>
+      </c>
+      <c r="D44" t="n">
+        <v>2407.381367641814</v>
+      </c>
+      <c r="E44" t="n">
+        <v>2741.855986968744</v>
+      </c>
+      <c r="F44" t="n">
+        <v>2910.660551435313</v>
+      </c>
+      <c r="G44" t="n">
+        <v>378825</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>very urban</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>decile 3</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>3626.014990956859</v>
+      </c>
+      <c r="D45" t="n">
+        <v>2437.123005159699</v>
+      </c>
+      <c r="E45" t="n">
+        <v>2831.721049640655</v>
+      </c>
+      <c r="F45" t="n">
+        <v>2931.645023849467</v>
+      </c>
+      <c r="G45" t="n">
+        <v>335820</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>very urban</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>decile 4</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>3757.803361000632</v>
+      </c>
+      <c r="D46" t="n">
+        <v>2658.307227391697</v>
+      </c>
+      <c r="E46" t="n">
+        <v>3079.403929706898</v>
+      </c>
+      <c r="F46" t="n">
+        <v>3143.729611951531</v>
+      </c>
+      <c r="G46" t="n">
+        <v>339790</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>very urban</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>decile 5</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>3970.066989034565</v>
+      </c>
+      <c r="D47" t="n">
+        <v>2728.530599995424</v>
+      </c>
+      <c r="E47" t="n">
+        <v>3339.891937522536</v>
+      </c>
+      <c r="F47" t="n">
+        <v>3344.595366018765</v>
+      </c>
+      <c r="G47" t="n">
+        <v>339365</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>very urban</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>decile 6</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>3460.790363030416</v>
+      </c>
+      <c r="D48" t="n">
+        <v>2534.800120772333</v>
+      </c>
+      <c r="E48" t="n">
+        <v>3039.895105463411</v>
+      </c>
+      <c r="F48" t="n">
+        <v>3018.845173682393</v>
+      </c>
+      <c r="G48" t="n">
+        <v>334730</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>very urban</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>decile 7</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>3619.446603697561</v>
+      </c>
+      <c r="D49" t="n">
+        <v>2749.128574791855</v>
+      </c>
+      <c r="E49" t="n">
+        <v>3280.973085183111</v>
+      </c>
+      <c r="F49" t="n">
+        <v>3232.63033721391</v>
+      </c>
+      <c r="G49" t="n">
+        <v>339950</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>very urban</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>decile 8</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>3796.786644305857</v>
+      </c>
+      <c r="D50" t="n">
+        <v>2873.11349614364</v>
+      </c>
+      <c r="E50" t="n">
+        <v>3405.414304786696</v>
+      </c>
+      <c r="F50" t="n">
+        <v>3370.182187505722</v>
+      </c>
+      <c r="G50" t="n">
+        <v>359560</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>very urban</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>decile 9</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>4046.342001754093</v>
+      </c>
+      <c r="D51" t="n">
+        <v>3186.675254862184</v>
+      </c>
+      <c r="E51" t="n">
+        <v>3748.175449472546</v>
+      </c>
+      <c r="F51" t="n">
+        <v>3682.342038890342</v>
+      </c>
+      <c r="G51" t="n">
+        <v>384185</v>
       </c>
     </row>
   </sheetData>

--- a/data_input/density_class_combo_emissions.xlsx
+++ b/data_input/density_class_combo_emissions.xlsx
@@ -477,16 +477,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5885.438713979452</v>
+        <v>4911.496665397945</v>
       </c>
       <c r="D2" t="n">
-        <v>3815.326299624254</v>
+        <v>3832.388957812942</v>
       </c>
       <c r="E2" t="n">
-        <v>4356.990681273705</v>
+        <v>4460.868559661682</v>
       </c>
       <c r="F2" t="n">
-        <v>4603.686594037779</v>
+        <v>4416.405685633563</v>
       </c>
       <c r="G2" t="n">
         <v>2254475</v>
@@ -504,16 +504,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7022.35421696803</v>
+        <v>7091.124522305787</v>
       </c>
       <c r="D3" t="n">
-        <v>3630.09418701205</v>
+        <v>3994.548276334268</v>
       </c>
       <c r="E3" t="n">
-        <v>4945.394340895863</v>
+        <v>4890.021147650991</v>
       </c>
       <c r="F3" t="n">
-        <v>5135.809271442951</v>
+        <v>5216.428773485509</v>
       </c>
       <c r="G3" t="n">
         <v>183240</v>
@@ -531,16 +531,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4798.163975956058</v>
+        <v>4733.062415568348</v>
       </c>
       <c r="D4" t="n">
-        <v>2755.057301259241</v>
+        <v>2943.381864269975</v>
       </c>
       <c r="E4" t="n">
-        <v>3587.449069498815</v>
+        <v>3482.771214268875</v>
       </c>
       <c r="F4" t="n">
-        <v>3682.029854053232</v>
+        <v>3660.496677094018</v>
       </c>
       <c r="G4" t="n">
         <v>629555</v>
@@ -558,16 +558,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6856.560316007463</v>
+        <v>5740.136885743651</v>
       </c>
       <c r="D5" t="n">
-        <v>4517.508062458724</v>
+        <v>4464.679503023975</v>
       </c>
       <c r="E5" t="n">
-        <v>4979.940841848915</v>
+        <v>5072.864022052945</v>
       </c>
       <c r="F5" t="n">
-        <v>5333.487515541005</v>
+        <v>5087.636108218379</v>
       </c>
       <c r="G5" t="n">
         <v>2077660</v>
@@ -585,16 +585,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6875.952690843332</v>
+        <v>7079.880374933086</v>
       </c>
       <c r="D6" t="n">
-        <v>3891.541550423678</v>
+        <v>4296.286589718811</v>
       </c>
       <c r="E6" t="n">
-        <v>5633.779993692066</v>
+        <v>5464.781080939631</v>
       </c>
       <c r="F6" t="n">
-        <v>5508.763557162785</v>
+        <v>5576.43228163279</v>
       </c>
       <c r="G6" t="n">
         <v>135380</v>
@@ -612,16 +612,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5490.845356833731</v>
+        <v>5298.232799341185</v>
       </c>
       <c r="D7" t="n">
-        <v>3441.688371424738</v>
+        <v>3671.8256170858</v>
       </c>
       <c r="E7" t="n">
-        <v>4502.323700768236</v>
+        <v>4387.737022256679</v>
       </c>
       <c r="F7" t="n">
-        <v>4484.295282448736</v>
+        <v>4436.383115235086</v>
       </c>
       <c r="G7" t="n">
         <v>442365</v>
@@ -639,16 +639,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5811.008847314267</v>
+        <v>5581.095721343929</v>
       </c>
       <c r="D8" t="n">
-        <v>4854.986454913957</v>
+        <v>4636.536377987034</v>
       </c>
       <c r="E8" t="n">
-        <v>5233.68324629469</v>
+        <v>5182.763905534606</v>
       </c>
       <c r="F8" t="n">
-        <v>5283.3404487044</v>
+        <v>5145.789977600044</v>
       </c>
       <c r="G8" t="n">
         <v>2156355</v>
@@ -666,16 +666,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6706.930190072303</v>
+        <v>6958.997753521457</v>
       </c>
       <c r="D9" t="n">
-        <v>4579.438194532134</v>
+        <v>4768.246960130776</v>
       </c>
       <c r="E9" t="n">
-        <v>5996.25455248341</v>
+        <v>5891.500796786215</v>
       </c>
       <c r="F9" t="n">
-        <v>5819.719372392814</v>
+        <v>5877.561576806165</v>
       </c>
       <c r="G9" t="n">
         <v>155555</v>
@@ -693,16 +693,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5991.233202686336</v>
+        <v>5994.614475497911</v>
       </c>
       <c r="D10" t="n">
-        <v>3860.128216891741</v>
+        <v>3985.362503925388</v>
       </c>
       <c r="E10" t="n">
-        <v>5078.548332588484</v>
+        <v>4739.562862882447</v>
       </c>
       <c r="F10" t="n">
-        <v>5002.114521188762</v>
+        <v>4864.775676297048</v>
       </c>
       <c r="G10" t="n">
         <v>248880</v>
@@ -720,16 +720,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5585.02341419302</v>
+        <v>4825.426378082513</v>
       </c>
       <c r="D11" t="n">
-        <v>3642.814579523156</v>
+        <v>3728.5491915398</v>
       </c>
       <c r="E11" t="n">
-        <v>4326.264742248695</v>
+        <v>4418.212094654136</v>
       </c>
       <c r="F11" t="n">
-        <v>4470.091869553392</v>
+        <v>4347.599939732647</v>
       </c>
       <c r="G11" t="n">
         <v>2688645</v>
@@ -747,16 +747,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>8208.365989629841</v>
+        <v>8088.606815906125</v>
       </c>
       <c r="D12" t="n">
-        <v>4116.620398576352</v>
+        <v>4545.78052843883</v>
       </c>
       <c r="E12" t="n">
-        <v>5263.093465643761</v>
+        <v>5306.234450741997</v>
       </c>
       <c r="F12" t="n">
-        <v>5712.79332987343</v>
+        <v>5811.714061457236</v>
       </c>
       <c r="G12" t="n">
         <v>333340</v>
@@ -774,16 +774,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5929.426064892786</v>
+        <v>5589.101621420755</v>
       </c>
       <c r="D13" t="n">
-        <v>2555.855974029972</v>
+        <v>2772.082560444347</v>
       </c>
       <c r="E13" t="n">
-        <v>3243.709742277852</v>
+        <v>3229.65668305242</v>
       </c>
       <c r="F13" t="n">
-        <v>3743.175380869615</v>
+        <v>3705.124386992486</v>
       </c>
       <c r="G13" t="n">
         <v>1154980</v>
@@ -801,16 +801,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4468.895865610992</v>
+        <v>4694.689418447797</v>
       </c>
       <c r="D14" t="n">
-        <v>3334.619606783634</v>
+        <v>3537.607176466083</v>
       </c>
       <c r="E14" t="n">
-        <v>4051.884041148074</v>
+        <v>4012.144686159684</v>
       </c>
       <c r="F14" t="n">
-        <v>3976.820888672693</v>
+        <v>4064.146491808312</v>
       </c>
       <c r="G14" t="n">
         <v>1732915</v>
@@ -828,16 +828,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>9377.689862340778</v>
+        <v>9016.349284731297</v>
       </c>
       <c r="D15" t="n">
-        <v>4237.505181626087</v>
+        <v>4226.140667004545</v>
       </c>
       <c r="E15" t="n">
-        <v>4699.19515688581</v>
+        <v>4794.068730447932</v>
       </c>
       <c r="F15" t="n">
-        <v>5753.396339434621</v>
+        <v>5707.656853157927</v>
       </c>
       <c r="G15" t="n">
         <v>684640</v>
@@ -855,16 +855,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>6263.467842375323</v>
+        <v>6169.284248133609</v>
       </c>
       <c r="D16" t="n">
-        <v>2396.895055655953</v>
+        <v>2605.059751634401</v>
       </c>
       <c r="E16" t="n">
-        <v>2859.941984478597</v>
+        <v>2924.00567414758</v>
       </c>
       <c r="F16" t="n">
-        <v>3595.061716747118</v>
+        <v>3655.588837015792</v>
       </c>
       <c r="G16" t="n">
         <v>1361870</v>

--- a/data_input/density_class_combo_emissions.xlsx
+++ b/data_input/density_class_combo_emissions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,7 +436,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>tenure_lab</t>
+          <t>inc_lab</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -473,23 +473,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>owner occupied</t>
+          <t>51-90%</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4911.496665397945</v>
+        <v>4453.144266790459</v>
       </c>
       <c r="D2" t="n">
-        <v>3832.388957812942</v>
+        <v>3646.431619576658</v>
       </c>
       <c r="E2" t="n">
-        <v>4460.868559661682</v>
+        <v>4115.614891975494</v>
       </c>
       <c r="F2" t="n">
-        <v>4416.405685633563</v>
+        <v>4082.701417579527</v>
       </c>
       <c r="G2" t="n">
-        <v>2254475</v>
+        <v>1460025</v>
       </c>
     </row>
     <row r="3">
@@ -500,23 +500,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>private rental</t>
+          <t>91-99%</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7091.124522305787</v>
+        <v>5329.527485225737</v>
       </c>
       <c r="D3" t="n">
-        <v>3994.548276334268</v>
+        <v>4613.654804490987</v>
       </c>
       <c r="E3" t="n">
-        <v>4890.021147650991</v>
+        <v>5016.472643173143</v>
       </c>
       <c r="F3" t="n">
-        <v>5216.428773485509</v>
+        <v>4994.031894015753</v>
       </c>
       <c r="G3" t="n">
-        <v>183240</v>
+        <v>321830</v>
       </c>
     </row>
     <row r="4">
@@ -527,50 +527,50 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>social rental</t>
+          <t>poorest 50%</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4733.062415568348</v>
+        <v>4310.389520408152</v>
       </c>
       <c r="D4" t="n">
-        <v>2943.381864269975</v>
+        <v>3030.934174804303</v>
       </c>
       <c r="E4" t="n">
-        <v>3482.771214268875</v>
+        <v>3597.287586063643</v>
       </c>
       <c r="F4" t="n">
-        <v>3660.496677094018</v>
+        <v>3633.974716834935</v>
       </c>
       <c r="G4" t="n">
-        <v>629555</v>
+        <v>1254925</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>low suburban</t>
+          <t>high suburban</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>owner occupied</t>
+          <t>top 1%</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5740.136885743651</v>
+        <v>6720.365585093559</v>
       </c>
       <c r="D5" t="n">
-        <v>4464.679503023975</v>
+        <v>5640.888183672378</v>
       </c>
       <c r="E5" t="n">
-        <v>5072.864022052945</v>
+        <v>6251.912747171431</v>
       </c>
       <c r="F5" t="n">
-        <v>5087.636108218379</v>
+        <v>6216.2698157772</v>
       </c>
       <c r="G5" t="n">
-        <v>2077660</v>
+        <v>31610</v>
       </c>
     </row>
     <row r="6">
@@ -581,23 +581,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>private rental</t>
+          <t>51-90%</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7079.880374933086</v>
+        <v>5467.86178759557</v>
       </c>
       <c r="D6" t="n">
-        <v>4296.286589718811</v>
+        <v>4486.194038712213</v>
       </c>
       <c r="E6" t="n">
-        <v>5464.781080939631</v>
+        <v>4886.520804853755</v>
       </c>
       <c r="F6" t="n">
-        <v>5576.43228163279</v>
+        <v>4931.774359003823</v>
       </c>
       <c r="G6" t="n">
-        <v>135380</v>
+        <v>1300790</v>
       </c>
     </row>
     <row r="7">
@@ -608,77 +608,77 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>social rental</t>
+          <t>91-99%</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5298.232799341185</v>
+        <v>6000.931866518476</v>
       </c>
       <c r="D7" t="n">
-        <v>3671.8256170858</v>
+        <v>5072.593238091414</v>
       </c>
       <c r="E7" t="n">
-        <v>4387.737022256679</v>
+        <v>5502.938458333406</v>
       </c>
       <c r="F7" t="n">
-        <v>4436.383115235086</v>
+        <v>5519.850505319175</v>
       </c>
       <c r="G7" t="n">
-        <v>442365</v>
+        <v>299315</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>rural</t>
+          <t>low suburban</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>owner occupied</t>
+          <t>poorest 50%</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5581.095721343929</v>
+        <v>4685.663852350664</v>
       </c>
       <c r="D8" t="n">
-        <v>4636.536377987034</v>
+        <v>3455.406319909788</v>
       </c>
       <c r="E8" t="n">
-        <v>5182.763905534606</v>
+        <v>4128.775579663262</v>
       </c>
       <c r="F8" t="n">
-        <v>5145.789977600044</v>
+        <v>4099.655332896744</v>
       </c>
       <c r="G8" t="n">
-        <v>2156355</v>
+        <v>1022635</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>rural</t>
+          <t>low suburban</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>private rental</t>
+          <t>top 1%</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6958.997753521457</v>
+        <v>5962.187195453771</v>
       </c>
       <c r="D9" t="n">
-        <v>4768.246960130776</v>
+        <v>5061.975387101282</v>
       </c>
       <c r="E9" t="n">
-        <v>5891.500796786215</v>
+        <v>5525.929044072946</v>
       </c>
       <c r="F9" t="n">
-        <v>5877.561576806165</v>
+        <v>5519.005167675236</v>
       </c>
       <c r="G9" t="n">
-        <v>155555</v>
+        <v>33240</v>
       </c>
     </row>
     <row r="10">
@@ -689,185 +689,320 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>social rental</t>
+          <t>51-90%</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5994.614475497911</v>
+        <v>4873.18152700621</v>
       </c>
       <c r="D10" t="n">
-        <v>3985.362503925388</v>
+        <v>4279.98135622386</v>
       </c>
       <c r="E10" t="n">
-        <v>4739.562862882447</v>
+        <v>4597.352975827813</v>
       </c>
       <c r="F10" t="n">
-        <v>4864.775676297048</v>
+        <v>4586.967208721424</v>
       </c>
       <c r="G10" t="n">
-        <v>248880</v>
+        <v>1252035</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>urban</t>
+          <t>rural</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>owner occupied</t>
+          <t>91-99%</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4825.426378082513</v>
+        <v>6014.747791854893</v>
       </c>
       <c r="D11" t="n">
-        <v>3728.5491915398</v>
+        <v>5466.760807091032</v>
       </c>
       <c r="E11" t="n">
-        <v>4418.212094654136</v>
+        <v>5687.72771419366</v>
       </c>
       <c r="F11" t="n">
-        <v>4347.599939732647</v>
+        <v>5714.241006833312</v>
       </c>
       <c r="G11" t="n">
-        <v>2688645</v>
+        <v>338570</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>urban</t>
+          <t>rural</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>private rental</t>
+          <t>poorest 50%</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>8088.606815906125</v>
+        <v>5212.468664148926</v>
       </c>
       <c r="D12" t="n">
-        <v>4545.78052843883</v>
+        <v>4024.679710318929</v>
       </c>
       <c r="E12" t="n">
-        <v>5306.234450741997</v>
+        <v>4710.040300729996</v>
       </c>
       <c r="F12" t="n">
-        <v>5811.714061457236</v>
+        <v>4664.307243981962</v>
       </c>
       <c r="G12" t="n">
-        <v>333340</v>
+        <v>931530</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>urban</t>
+          <t>rural</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>social rental</t>
+          <t>top 1%</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5589.101621420755</v>
+        <v>6231.775414810246</v>
       </c>
       <c r="D13" t="n">
-        <v>2772.082560444347</v>
+        <v>5317.831319386308</v>
       </c>
       <c r="E13" t="n">
-        <v>3229.65668305242</v>
+        <v>5749.50764497883</v>
       </c>
       <c r="F13" t="n">
-        <v>3705.124386992486</v>
+        <v>5762.155506038554</v>
       </c>
       <c r="G13" t="n">
-        <v>1154980</v>
+        <v>39515</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>very urban</t>
+          <t>urban</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>owner occupied</t>
+          <t>51-90%</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4694.689418447797</v>
+        <v>4435.780155409547</v>
       </c>
       <c r="D14" t="n">
-        <v>3537.607176466083</v>
+        <v>3552.642230397776</v>
       </c>
       <c r="E14" t="n">
-        <v>4012.144686159684</v>
+        <v>4096.373602690445</v>
       </c>
       <c r="F14" t="n">
-        <v>4064.146491808312</v>
+        <v>4045.292397797053</v>
       </c>
       <c r="G14" t="n">
-        <v>1732915</v>
+        <v>1834780</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>very urban</t>
+          <t>urban</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>private rental</t>
+          <t>91-99%</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>9016.349284731297</v>
+        <v>5157.330774527875</v>
       </c>
       <c r="D15" t="n">
-        <v>4226.140667004545</v>
+        <v>4417.269085192635</v>
       </c>
       <c r="E15" t="n">
-        <v>4794.068730447932</v>
+        <v>4931.809868811791</v>
       </c>
       <c r="F15" t="n">
-        <v>5707.656853157927</v>
+        <v>4859.554899336023</v>
       </c>
       <c r="G15" t="n">
-        <v>684640</v>
+        <v>400205</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>urban</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>poorest 50%</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>4202.389612773768</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2817.369555930721</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3300.284776044617</v>
+      </c>
+      <c r="F16" t="n">
+        <v>3405.082180198431</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1905790</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>urban</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>top 1%</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>9306.47532605302</v>
+      </c>
+      <c r="D17" t="n">
+        <v>8145.191972325329</v>
+      </c>
+      <c r="E17" t="n">
+        <v>8545.517828344866</v>
+      </c>
+      <c r="F17" t="n">
+        <v>8635.67573876702</v>
+      </c>
+      <c r="G17" t="n">
+        <v>37940</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>very urban</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>social rental</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>6169.284248133609</v>
-      </c>
-      <c r="D16" t="n">
-        <v>2605.059751634401</v>
-      </c>
-      <c r="E16" t="n">
-        <v>2924.00567414758</v>
-      </c>
-      <c r="F16" t="n">
-        <v>3655.588837015792</v>
-      </c>
-      <c r="G16" t="n">
-        <v>1361870</v>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>51-90%</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>3940.657793975894</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3028.003469168721</v>
+      </c>
+      <c r="E18" t="n">
+        <v>3394.623494181177</v>
+      </c>
+      <c r="F18" t="n">
+        <v>3439.477062876742</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1418650</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>very urban</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>91-99%</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>4884.409403338443</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3821.926375146114</v>
+      </c>
+      <c r="E19" t="n">
+        <v>4201.973637091087</v>
+      </c>
+      <c r="F19" t="n">
+        <v>4277.570763166683</v>
+      </c>
+      <c r="G19" t="n">
+        <v>392465</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>very urban</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>poorest 50%</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>3927.744151723606</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2596.928732785874</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2895.308286387439</v>
+      </c>
+      <c r="F20" t="n">
+        <v>3078.822364321089</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1925210</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>very urban</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>top 1%</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>8053.363818392081</v>
+      </c>
+      <c r="D21" t="n">
+        <v>6556.834847650395</v>
+      </c>
+      <c r="E21" t="n">
+        <v>7243.269085600765</v>
+      </c>
+      <c r="F21" t="n">
+        <v>7274.184209311002</v>
+      </c>
+      <c r="G21" t="n">
+        <v>46530</v>
       </c>
     </row>
   </sheetData>
